--- a/p6_deployment/data/france/missing/data_understanding/df_match_miss.xlsx
+++ b/p6_deployment/data/france/missing/data_understanding/df_match_miss.xlsx
@@ -1041,7 +1041,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>zB2j3Yv</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>SIFtcwD</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4537,7 +4537,12 @@
           <t>19.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Stadium Municipal
@@ -4790,7 +4795,7 @@
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -4800,7 +4805,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -5110,7 +5115,7 @@
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -5120,7 +5125,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5422,7 +5427,7 @@
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>SIFtcwD</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -5432,7 +5437,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5734,7 +5739,7 @@
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -5744,7 +5749,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -6046,7 +6051,7 @@
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -6056,7 +6061,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -6358,7 +6363,7 @@
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -6368,7 +6373,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6670,7 +6675,7 @@
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -6680,7 +6685,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -6974,7 +6979,7 @@
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -6984,7 +6989,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -7286,7 +7291,7 @@
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -7296,7 +7301,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -7598,7 +7603,7 @@
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -7608,7 +7613,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -7910,7 +7915,7 @@
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
@@ -7920,7 +7925,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>SIFtcwD</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -8222,7 +8227,7 @@
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
@@ -8232,7 +8237,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -8268,12 +8273,7 @@
           <t>06.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Stade Pierre-Mauroy
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>K6b7RoB</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>K6b7RoB</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>6FKPxxg</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>lb31RXz</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>OpNm82M</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="BG60" t="inlineStr">
         <is>
-          <t>h89kUbu</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="BH60" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>bauuckz</t>
+          <t>bauuckzB</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>zB2j3Yv</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>xt8jqdt</t>
+          <t>xt8jqdte</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>fm0Qb28</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>Q9EVqFe</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>boLlrzT</t>
+          <t>boLlrzTH</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>feuQknK</t>
+          <t>feuQknKS</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
@@ -20345,7 +20345,7 @@
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>dS1CBpl</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>4vG8dmr</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
@@ -20641,7 +20641,7 @@
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>Ys1Pb7w</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>QuOmnHM</t>
+          <t>QuOmnHMq</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>Cp0gM1r</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>bXIqj1k</t>
+          <t>bXIqj1ke</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>SIiBpBr</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>Cp0gM1r</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>feuQknK</t>
+          <t>feuQknKS</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>dS1CBpl</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>OpNm82M</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>SIiBpBr</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="BG71" t="inlineStr">
         <is>
-          <t>6FKPxxg</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="BH71" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>h89kUbu</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>xt8jqdt</t>
+          <t>xt8jqdte</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>lb31RXz</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>Q9EVqFe</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>Ys1Pb7w</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>bXIqj1k</t>
+          <t>bXIqj1ke</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>zB2j3Yv</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>4vG8dmr</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>fm0Qb28</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>bauuckz</t>
+          <t>bauuckzB</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
@@ -24189,7 +24189,7 @@
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>boLlrzT</t>
+          <t>boLlrzTH</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
@@ -24485,7 +24485,7 @@
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>QuOmnHM</t>
+          <t>QuOmnHMq</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
